--- a/artfynd/A 22983-2024 artfynd.xlsx
+++ b/artfynd/A 22983-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY36"/>
+  <dimension ref="A1:AY47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121760234</v>
+        <v>125399220</v>
       </c>
       <c r="B2" t="n">
-        <v>79726</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>564580</v>
+        <v>564519</v>
       </c>
       <c r="R2" t="n">
-        <v>6991851</v>
+        <v>6991683</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +740,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På toppknäckt granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,27 +775,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Joel Olsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Joel Olsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121760285</v>
+        <v>125426264</v>
       </c>
       <c r="B3" t="n">
-        <v>57374</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,37 +798,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>564577</v>
+        <v>564514</v>
       </c>
       <c r="R3" t="n">
-        <v>6991812</v>
+        <v>6991688</v>
       </c>
       <c r="S3" t="n">
-        <v>75</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,17 +852,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2025-05-25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Troliga ringhack på tall</t>
+          <t>2025-05-25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,27 +872,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Joel Olsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Joel Olsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121760201</v>
+        <v>125398362</v>
       </c>
       <c r="B4" t="n">
-        <v>79726</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,37 +895,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>564522</v>
+        <v>564453</v>
       </c>
       <c r="R4" t="n">
-        <v>6991757</v>
+        <v>6991691</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -954,12 +949,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -974,27 +984,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Joel Olsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Joel Olsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121760289</v>
+        <v>125398876</v>
       </c>
       <c r="B5" t="n">
-        <v>78645</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1002,37 +1007,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>564537</v>
+        <v>564507</v>
       </c>
       <c r="R5" t="n">
-        <v>6991776</v>
+        <v>6991687</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1056,12 +1061,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På två granlågor i lågabröt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1076,27 +1096,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Joel Olsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Joel Olsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121760206</v>
+        <v>125426261</v>
       </c>
       <c r="B6" t="n">
-        <v>79726</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1104,37 +1119,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>564537</v>
+        <v>564561</v>
       </c>
       <c r="R6" t="n">
-        <v>6991776</v>
+        <v>6991726</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1158,17 +1173,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2025-05-25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Lunglav även på granar</t>
+          <t>2025-05-25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1183,27 +1193,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Joel Olsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Joel Olsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121760194</v>
+        <v>122227597</v>
       </c>
       <c r="B7" t="n">
-        <v>79726</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1211,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>564554</v>
+        <v>564522</v>
       </c>
       <c r="R7" t="n">
-        <v>6991781</v>
+        <v>6991757</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1265,12 +1270,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2025-01-19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2025-01-19</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Skrovellav på granit</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1297,15 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121798021</v>
+        <v>122227661</v>
       </c>
       <c r="B8" t="n">
-        <v>79726</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1313,21 +1318,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,13 +1342,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>564477</v>
+        <v>564599</v>
       </c>
       <c r="R8" t="n">
-        <v>6991714</v>
+        <v>6991793</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1367,12 +1372,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2025-01-19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2025-01-19</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På granit</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1399,37 +1409,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122227567</v>
+        <v>122227693</v>
       </c>
       <c r="B9" t="n">
-        <v>98240</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>564533</v>
+        <v>564520</v>
       </c>
       <c r="R9" t="n">
-        <v>6991752</v>
+        <v>6991746</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1475,6 +1480,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-01-19</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På granit</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1501,53 +1511,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122227597</v>
+        <v>125426270</v>
       </c>
       <c r="B10" t="n">
-        <v>79738</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>2809</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>564522</v>
+        <v>564544</v>
       </c>
       <c r="R10" t="n">
-        <v>6991757</v>
+        <v>6991700</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1571,17 +1576,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-01-19</t>
+          <t>2025-05-25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-01-19</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Skrovellav på granit</t>
+          <t>2025-05-25</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1596,49 +1596,44 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Joel Olsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Joel Olsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122227581</v>
+        <v>125438544</v>
       </c>
       <c r="B11" t="n">
-        <v>98240</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1648,13 +1643,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>564497</v>
+        <v>564517</v>
       </c>
       <c r="R11" t="n">
-        <v>6991715</v>
+        <v>6991669</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1678,12 +1673,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-01-19</t>
+          <t>2025-05-25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-01-19</t>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1698,68 +1698,60 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Joel Olsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Joel Olsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122227671</v>
+        <v>121760289</v>
       </c>
       <c r="B12" t="n">
-        <v>79737</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>564587</v>
+        <v>564537</v>
       </c>
       <c r="R12" t="n">
-        <v>6991775</v>
+        <v>6991776</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1783,12 +1775,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-01-19</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-01-19</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1797,7 +1789,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1816,53 +1807,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122227587</v>
+        <v>125426251</v>
       </c>
       <c r="B13" t="n">
-        <v>98240</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>564524</v>
+        <v>564469</v>
       </c>
       <c r="R13" t="n">
-        <v>6991706</v>
+        <v>6991678</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1886,12 +1872,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-01-19</t>
+          <t>2025-05-25</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-01-19</t>
+          <t>2025-05-25</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1906,27 +1892,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Joel Olsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Joel Olsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122227693</v>
+        <v>125399781</v>
       </c>
       <c r="B14" t="n">
-        <v>79738</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1934,37 +1915,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>564520</v>
+        <v>564559</v>
       </c>
       <c r="R14" t="n">
-        <v>6991746</v>
+        <v>6991743</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1988,17 +1974,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-01-19</t>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-01-19</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På granit</t>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2013,65 +2004,60 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Joel Olsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Joel Olsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122227560</v>
+        <v>125399514</v>
       </c>
       <c r="B15" t="n">
-        <v>98240</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>564605</v>
+        <v>564559</v>
       </c>
       <c r="R15" t="n">
-        <v>6991859</v>
+        <v>6991707</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2095,12 +2081,27 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-01-19</t>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-01-19</t>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På kolad ved på gammal tallhögstubbe i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2115,49 +2116,44 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Joel Olsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Joel Olsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122227568</v>
+        <v>121760194</v>
       </c>
       <c r="B16" t="n">
-        <v>98240</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2167,13 +2163,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>564519</v>
+        <v>564554</v>
       </c>
       <c r="R16" t="n">
-        <v>6991735</v>
+        <v>6991781</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2197,12 +2193,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-01-19</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-01-19</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2229,15 +2225,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122227607</v>
+        <v>121760201</v>
       </c>
       <c r="B17" t="n">
-        <v>79737</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2269,13 +2260,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>564537</v>
+        <v>564522</v>
       </c>
       <c r="R17" t="n">
-        <v>6991743</v>
+        <v>6991757</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2299,12 +2290,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-01-19</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-01-19</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2331,37 +2322,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122227563</v>
+        <v>121760206</v>
       </c>
       <c r="B18" t="n">
-        <v>98240</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2371,10 +2357,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>564580</v>
+        <v>564537</v>
       </c>
       <c r="R18" t="n">
-        <v>6991851</v>
+        <v>6991776</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2401,12 +2387,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-01-19</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-01-19</t>
+          <t>2024-12-27</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Lunglav även på granar</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2433,37 +2424,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122227576</v>
+        <v>121760234</v>
       </c>
       <c r="B19" t="n">
-        <v>98240</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2473,13 +2459,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>564535</v>
+        <v>564580</v>
       </c>
       <c r="R19" t="n">
-        <v>6991761</v>
+        <v>6991851</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2503,12 +2489,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-01-19</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-01-19</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2535,10 +2521,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125399514</v>
+        <v>121798021</v>
       </c>
       <c r="B20" t="n">
-        <v>79590</v>
+        <v>80432</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2546,37 +2532,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Stortjärndalen, Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>564559</v>
+        <v>564477</v>
       </c>
       <c r="R20" t="n">
-        <v>6991707</v>
+        <v>6991714</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2600,27 +2586,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>14:43</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>14:43</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På kolad ved på gammal tallhögstubbe i gammal barrblandskog</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2635,74 +2606,60 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Joel Olsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Joel Olsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125399518</v>
+        <v>122227607</v>
       </c>
       <c r="B21" t="n">
-        <v>98339</v>
+        <v>80432</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Stortjärndalen, Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>564559</v>
+        <v>564537</v>
       </c>
       <c r="R21" t="n">
         <v>6991743</v>
       </c>
       <c r="S21" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2726,22 +2683,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>14:44</t>
+          <t>2025-01-19</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>14:44</t>
+          <t>2025-01-19</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2756,74 +2703,60 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Joel Olsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Joel Olsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125399292</v>
+        <v>122227660</v>
       </c>
       <c r="B22" t="n">
-        <v>98339</v>
+        <v>80432</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Stortjärndalen, Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>564535</v>
+        <v>564599</v>
       </c>
       <c r="R22" t="n">
-        <v>6991702</v>
+        <v>6991793</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2847,27 +2780,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>14:39</t>
+          <t>2025-01-19</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>14:39</t>
+          <t>2025-01-19</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På marken i gammal barrblandskog</t>
+          <t>På granit</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2882,69 +2805,63 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Joel Olsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Joel Olsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125399660</v>
+        <v>122227671</v>
       </c>
       <c r="B23" t="n">
-        <v>80111</v>
+        <v>80432</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Stortjärndalen, Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>564559</v>
+        <v>564587</v>
       </c>
       <c r="R23" t="n">
-        <v>6991743</v>
+        <v>6991775</v>
       </c>
       <c r="S23" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2968,22 +2885,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>14:49</t>
+          <t>2025-01-19</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>14:49</t>
+          <t>2025-01-19</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2992,28 +2899,29 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Joel Olsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Joel Olsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125399762</v>
+        <v>122227681</v>
       </c>
       <c r="B24" t="n">
-        <v>78731</v>
+        <v>80432</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3021,37 +2929,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Stortjärndalen, Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>564559</v>
+        <v>564616</v>
       </c>
       <c r="R24" t="n">
-        <v>6991743</v>
+        <v>6991805</v>
       </c>
       <c r="S24" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3075,22 +2983,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>14:54</t>
+          <t>2025-01-19</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>14:54</t>
+          <t>2025-01-19</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3105,12 +3003,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Joel Olsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Joel Olsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3120,7 +3018,7 @@
         <v>125399628</v>
       </c>
       <c r="B25" t="n">
-        <v>80075</v>
+        <v>80432</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3229,10 +3127,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125399450</v>
+        <v>125399646</v>
       </c>
       <c r="B26" t="n">
-        <v>78731</v>
+        <v>80432</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3240,21 +3138,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3264,10 +3162,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>564549</v>
+        <v>564526</v>
       </c>
       <c r="R26" t="n">
-        <v>6991719</v>
+        <v>6991737</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3299,7 +3197,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3309,12 +3207,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal tallhögstubbe</t>
+          <t>På gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3341,10 +3239,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125399646</v>
+        <v>125426273</v>
       </c>
       <c r="B27" t="n">
-        <v>80075</v>
+        <v>80432</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3372,17 +3270,17 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>564526</v>
+        <v>564561</v>
       </c>
       <c r="R27" t="n">
-        <v>6991737</v>
+        <v>6991770</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3409,24 +3307,9 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>14:49</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>14:49</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3441,22 +3324,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125399781</v>
+        <v>125438547</v>
       </c>
       <c r="B28" t="n">
-        <v>78730</v>
+        <v>80432</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3464,42 +3347,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Stortjärndalen, Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>564559</v>
+        <v>564543</v>
       </c>
       <c r="R28" t="n">
-        <v>6991743</v>
+        <v>6991694</v>
       </c>
       <c r="S28" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3526,19 +3404,14 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>14:54</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>14:54</t>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3565,42 +3438,42 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125399726</v>
+        <v>125399660</v>
       </c>
       <c r="B29" t="n">
-        <v>98339</v>
+        <v>80468</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3609,13 +3482,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>564572</v>
+        <v>564559</v>
       </c>
       <c r="R29" t="n">
-        <v>6991773</v>
+        <v>6991743</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3644,7 +3517,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3654,7 +3527,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3669,50 +3542,50 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125399679</v>
+        <v>125399613</v>
       </c>
       <c r="B30" t="n">
-        <v>80035</v>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3721,13 +3594,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>564559</v>
+        <v>564538</v>
       </c>
       <c r="R30" t="n">
-        <v>6991743</v>
+        <v>6991736</v>
       </c>
       <c r="S30" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3756,7 +3629,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3766,7 +3639,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gammal tall i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3781,22 +3659,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125426275</v>
+        <v>124048188</v>
       </c>
       <c r="B31" t="n">
-        <v>80035</v>
+        <v>57132</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3804,37 +3682,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>229497</v>
+        <v>102612</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>564567</v>
+        <v>564610</v>
       </c>
       <c r="R31" t="n">
-        <v>6991777</v>
+        <v>6991760</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3858,12 +3741,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
+          <t>2025-04-13</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
+          <t>2025-04-13</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3878,60 +3761,60 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Joel Olsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Joel Olsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125426270</v>
+        <v>122227560</v>
       </c>
       <c r="B32" t="n">
-        <v>95572</v>
+        <v>99118</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2809</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>564544</v>
+        <v>564605</v>
       </c>
       <c r="R32" t="n">
-        <v>6991700</v>
+        <v>6991859</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3955,12 +3838,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
+          <t>2025-01-19</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
+          <t>2025-01-19</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3975,22 +3858,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Joel Olsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Joel Olsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125426261</v>
+        <v>122227563</v>
       </c>
       <c r="B33" t="n">
-        <v>91686</v>
+        <v>99118</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3998,37 +3881,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>564561</v>
+        <v>564580</v>
       </c>
       <c r="R33" t="n">
-        <v>6991726</v>
+        <v>6991851</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4052,12 +3935,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
+          <t>2025-01-19</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
+          <t>2025-01-19</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4072,44 +3955,44 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Joel Olsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Joel Olsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125438547</v>
+        <v>122227567</v>
       </c>
       <c r="B34" t="n">
-        <v>80075</v>
+        <v>99118</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4119,13 +4002,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>564543</v>
+        <v>564533</v>
       </c>
       <c r="R34" t="n">
-        <v>6991694</v>
+        <v>6991752</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4149,17 +4032,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
+          <t>2025-01-19</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>På sälg</t>
+          <t>2025-01-19</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4174,60 +4052,60 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Joel Olsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Joel Olsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125426273</v>
+        <v>122227568</v>
       </c>
       <c r="B35" t="n">
-        <v>80075</v>
+        <v>99118</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>564561</v>
+        <v>564519</v>
       </c>
       <c r="R35" t="n">
-        <v>6991770</v>
+        <v>6991735</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4251,12 +4129,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
+          <t>2025-01-19</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
+          <t>2025-01-19</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4271,65 +4149,60 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Joel Olsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Joel Olsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125399613</v>
+        <v>122227576</v>
       </c>
       <c r="B36" t="n">
-        <v>57657</v>
+        <v>99118</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Stortjärndalen, Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>564538</v>
+        <v>564535</v>
       </c>
       <c r="R36" t="n">
-        <v>6991736</v>
+        <v>6991761</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4353,27 +4226,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>14:47</t>
+          <t>2025-01-19</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>14:47</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gammal tall i gammal barrblandskog</t>
+          <t>2025-01-19</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4388,15 +4246,1203 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>122227581</v>
+      </c>
+      <c r="B37" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Stortjärndalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>564497</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6991715</v>
+      </c>
+      <c r="S37" t="n">
+        <v>20</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-01-19</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-01-19</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>122227587</v>
+      </c>
+      <c r="B38" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Stortjärndalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>564524</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6991706</v>
+      </c>
+      <c r="S38" t="n">
+        <v>20</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-01-19</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-01-19</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>125399292</v>
+      </c>
+      <c r="B39" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Stortjärndalen, Stortjärndalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>564535</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6991702</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>På marken i gammal barrblandskog</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
           <t>Fredrik Jonsson</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
+      <c r="AX39" t="inlineStr">
         <is>
           <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
-      <c r="AY36" t="inlineStr"/>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>125399518</v>
+      </c>
+      <c r="B40" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Stortjärndalen, Stortjärndalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>564559</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6991743</v>
+      </c>
+      <c r="S40" t="n">
+        <v>12</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>125399726</v>
+      </c>
+      <c r="B41" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Stortjärndalen, Stortjärndalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>564572</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6991773</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>125426276</v>
+      </c>
+      <c r="B42" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>..., Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>564534</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6991686</v>
+      </c>
+      <c r="S42" t="n">
+        <v>15</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>125426249</v>
+      </c>
+      <c r="B43" t="n">
+        <v>106229</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>..., Jmt</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>564520</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6991682</v>
+      </c>
+      <c r="S43" t="n">
+        <v>15</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>125399450</v>
+      </c>
+      <c r="B44" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Stortjärndalen, Stortjärndalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>564549</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6991719</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>På kolad ved på gammal tallhögstubbe</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>125399762</v>
+      </c>
+      <c r="B45" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Stortjärndalen, Stortjärndalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>564559</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6991743</v>
+      </c>
+      <c r="S45" t="n">
+        <v>11</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>125399679</v>
+      </c>
+      <c r="B46" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Stortjärndalen, Stortjärndalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>564559</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6991743</v>
+      </c>
+      <c r="S46" t="n">
+        <v>11</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>125426275</v>
+      </c>
+      <c r="B47" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>..., Jmt</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>564567</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6991777</v>
+      </c>
+      <c r="S47" t="n">
+        <v>15</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
